--- a/文档/502采购清单(可勾选).xlsx
+++ b/文档/502采购清单(可勾选).xlsx
@@ -1024,49 +1024,49 @@
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
-      <c r="B13" s="8" t="n">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>扩展</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>红外对射 / 槽型光耦（做滴速才买）</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>槽型光耦 红外对射 计数传感器</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>1 个</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>★必须</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>滴速</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>红外对射（分体式：发射 + 接收各一个）</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>红外对射 对管 光电传感器 模块 3.3V 5V</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>A1「滴速」还没定做不做；现在只在引脚表里预留 PB12 + 3P 排针。</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>现在别买。等确认做滴速再下单，否则白花钱</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>滴速是课题要求之一（2026-10-22 导师确认要做）；每落一滴遮断一次光路，靠外部中断计数。</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>★必须【分体式】发射+接收各一个 —— 槽型光耦不可用：槽口约 5mm，滴壶直径约 20mm 卡不进去；选带比较器的数字输出模块，3.3~5V 供电、输出接 PB12；固定用泡棉+夹子并加遮光罩防环境光</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1215,14 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>必买 7 项合计（元）</t>
+          <t>必买 8 项合计（元）</t>
         </is>
       </c>
       <c r="H17" s="11" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>

--- a/文档/502采购清单(可勾选).xlsx
+++ b/文档/502采购清单(可勾选).xlsx
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>★必须【分体式】发射+接收各一个 —— 槽型光耦不可用：槽口约 5mm，滴壶直径约 20mm 卡不进去；选带比较器的数字输出模块，3.3~5V 供电、输出接 PB12；固定用泡棉+夹子并加遮光罩防环境光</t>
+          <t>★必须【分体式】发射+接收各一个 —— 槽型光耦不可用：槽口约 5mm，滴壶直径约 20mm 卡不进去；★规格：3.3~5V 供电、带比较器【数字输出】、检测距离 ≥10cm、每头带 2.54 排针（发射 2 针、接收 3 针）；固定用泡棉+夹子并加遮光罩防环境光；若卖家有【夹扣式输液滴速传感器】成品也可考虑，但要先确认接口电平</t>
         </is>
       </c>
     </row>
